--- a/Software_List.xlsx
+++ b/Software_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{972E2874-9235-442B-A49D-2CA5CD54A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144CE1F9-E7A5-4FB6-A25C-A403349EE2AE}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{972E2874-9235-442B-A49D-2CA5CD54A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F170BE66-0263-4187-B975-80ADAA36D03A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4527B83-BCAD-4BFA-8DAD-1CF98F9F309B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C4527B83-BCAD-4BFA-8DAD-1CF98F9F309B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t>NUNIEAU</t>
   </si>
@@ -44,18 +44,6 @@
     <t>NUNIEAU: Logiciel de NUmérisation des enregistrements graphiques de NIveaux d’EAU - Expertises Territoires</t>
   </si>
   <si>
-    <t>Plot Digitiser</t>
-  </si>
-  <si>
-    <t>WebPlotDigtiser</t>
-  </si>
-  <si>
-    <t>Digitiseit</t>
-  </si>
-  <si>
-    <t>Digitigraph</t>
-  </si>
-  <si>
     <t>DigitGraph Spreadsheet and WebPlot Digitiser | Newton Excel Bach, not (just) an Excel Blog</t>
   </si>
   <si>
@@ -80,9 +68,6 @@
     <t xml:space="preserve">Engauge Digitizer Download - This open source, digitizing software converts an image file showing </t>
   </si>
   <si>
-    <t>Engauge Digitiser</t>
-  </si>
-  <si>
     <t>Digitisation Tool</t>
   </si>
   <si>
@@ -189,6 +174,24 @@
   </si>
   <si>
     <t>$20.00 (Free version available)</t>
+  </si>
+  <si>
+    <t>WebPlotDigtizer</t>
+  </si>
+  <si>
+    <t>DigitiseIt</t>
+  </si>
+  <si>
+    <t>Plot Digitizer</t>
+  </si>
+  <si>
+    <t>DigitGraph</t>
+  </si>
+  <si>
+    <t>Engauge Digitizer</t>
+  </si>
+  <si>
+    <t>GRABIT - File Exchange - MATLAB Central</t>
   </si>
 </sst>
 </file>
@@ -260,11 +263,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -605,18 +609,18 @@
   <cols>
     <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="98.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.4">
@@ -624,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -632,209 +636,211 @@
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -858,6 +864,7 @@
     <hyperlink ref="C19" r:id="rId17" display="https://mybiosoftware.com/windig-2-5-image-data-digitizer.html" xr:uid="{5F7B18DB-A697-41FA-985F-93C78DA28165}"/>
     <hyperlink ref="C20" r:id="rId18" display="http://www.graphreader.com/" xr:uid="{B889BC85-3699-40AE-8E51-8892E2E4CA08}"/>
     <hyperlink ref="C21" r:id="rId19" display="https://www.macintoshrepository.org/48321-graphclick-" xr:uid="{1BB8E78E-E95D-4AC2-913F-220F4478DF17}"/>
+    <hyperlink ref="C10" r:id="rId20" display="https://ww2.mathworks.cn/matlabcentral/fileexchange/7173-grabit" xr:uid="{37A451F2-A453-4F87-9AEE-99E33CF8CC7C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
